--- a/context_DB/LBN_context_db.xlsx
+++ b/context_DB/LBN_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,154 +648,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LB41</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">October 2024: An educational facility was destroyed by Israeli airstrikes. </t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Foreign Forces - Military</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Israeli Defence Forces</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Plane</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>LB11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Al Nabatieh</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>LB4</t>
+          <t>LB1</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Battles ---- Violence against civilians ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+          <t>Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Air/drone strike ---- Armed clash ---- Attack ---- Air/drone strike ---- Air/drone strike</t>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Military Forces of Israel (2022-) ---- Hezbollah ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Military Forces of Israel (2022-) ---- Civilians (Lebanon) ---- Hezbollah</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Refugees/IDPs (Lebanon) ---- Civilians (Lebanon)</t>
-        </is>
-      </c>
+          <t>Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Palestine) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Teachers (Lebanon) ---- Teachers (Lebanon) ---- Teachers (Lebanon) ---- Teachers (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Labor Group (Lebanon); Teachers (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Labor Group (Lebanon); Teachers (Lebanon) ---- Labor Group (Lebanon); Teachers (Lebanon) ---- Students (Lebanon) ---- Labor Group (Lebanon) ---- Refugees/IDPs (Palestine) ---- Labor Group (Lebanon); Public Schools Teachers Association; Teachers (Lebanon) ---- Public Schools Teachers Association; Teachers (Lebanon) ---- Labor Group (Lebanon); Teachers (Lebanon) ---- Students (Lebanon) ---- Public Schools Teachers Association; Teachers (Lebanon) ---- Public Schools Teachers Association; Teachers (Lebanon) ---- Public Schools Teachers Association; Teachers (Lebanon) ---- Public Schools Teachers Association; Teachers (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Public Schools Teachers Association; Teachers (Lebanon) ---- Teachers (Lebanon) ---- Teachers (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>On 15 October 2024, Israeli warplanes carried out an airstrike on a house near a school in Qalaouiye (Bint Jbeil, Al Nabatieh). The house was destroyed. Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 23 October 2024, Hezbollah fired several missiles targeting an Israeli infantry force near a school in Ramieh town (Bint Jbeil, Al Nabatieh). The Israeli military also fired artillery shells towards the town. The group announced it had achieved direct hits. IDF announced that during the clashes in Southern Lebanon on the day, 4 soldiers from the 2nd Carmeli Reserve Infantry Brigade were killed, which is coded to this location. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 10 March 2025, several Israeli soldiers moved to the entrance of Ramieh (Bint Jbeil, Al Nabatieh) and opened fire toward a local school, which had been converted into a service center following the war between Hezbollah and Israel. A group of individuals (likely displaced families) managed to escape unharmed. There were no casualties. ---- On 9 April 2025, an Israeli drone struck an area with a missile near a public school in Ramieh town (Bint Jbeil, Al Nabatieh). There were no casualties. ---- On 5 July 2025, an Israeli drone struck a car with a missile in Bent Jbeil city (Bint Jbeil, Al Nabatieh). A second Israeli drone targeted a van near the vocational school in the city. One individual was killed and two others were injured in the attack. The Israeli Defense Forces (IDF) claimed that the deceased was a member of Hezbollah's elite Radwan Force unit.</t>
+          <t>On 16 January 2024, retired teachers held a protest outside the Ministry of Education in Beirut - Mousseitbeh (Beirut) to demand a solution to their pension and salary crisis. ---- On 20 February 2024, retired teachers organized a protest in front of the parliament building in Beirut - Bachoura (Beirut, Beirut) to demand that the government funds the compensation fund for members of the teaching staff in private schools. ---- On 5 March 2024, contracted teachers at the Lebanese university staged a protest in front of the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut) to demand better working conditions. ---- On 15 March 2024, teachers from the Markaziya school carried out a protest in front of the Justice Palace in Beirut - Achrafieh (Beirut, Beirut). This comes following the controversial paper that was distributed at the school explaining the concept of gender to children. ---- On 28 March 2024, several individuals staged a protest in front of Al Khazen barracks in Verdun in Beirut - Ras Beirut (Beirut, Beirut) to demand the release of activist Khodr Anwar. Anwar was arrested following a decision from the Public Prosecutor in Beirut due to his participation in student protests against the embezzlement of funds by the Middle East Airlines company. ---- On 30 April 2024, around 300 university students protested inside and infront of the AUB campus in Beirut - Ras Beirut (Beirut, Beirut) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. Another university student protest took place in the Lebanese American University in Qoreitim. ---- On 30 April 2024, university students protested at the BAU campus in Tareeq Al Jdeedeh in Beirut - Mazraa (Beirut, Beirut) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. ---- On 30 April 2024, university students protested at the LIU campus in Beirut - Mousseitbeh (Beirut, Beirut) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. ---- On 30 April 2024, university students protested at the USJ campus in Beirut - Achrafieh (Beirut, Beirut) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. ---- On 30 April 2024, university students protested at the Haigazian university campus in Beirut - Minet el Hosn (Beirut, Beirut) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. ---- On 7 May 2024, dozens of university students protested at the American University of Beirut in Beirut - Ras Beirut (Beirut, Beirut) in support of Palestine and Gaza. They rallied against the continuous Israeli bombardment of Gaza. ---- On 13 May 2024, university teachers and contracted professors staged a protest in front of the UNESCO building in Beirut - Mousseitbeh (Beirut, Beirut) against working conditions. ---- On 15 May 2024, university students held a protest at the University Saint Joseph in Beirut - Achrafieh (Beirut, Beirut) against the continuous Israeli bombardment of Gaza. They rallied in support of Gaza. ---- On 15 May 2024, university students held a protest at the American University of Beirut in Beirut - Ras Beirut (Beirut, Beirut) against the continuous Israeli bombardment of Gaza. They rallied in support of Gaza. ---- On 23 May 2024, university students took to the streets in front of the Beirut Arab University in Beirut - Mazraa (Beirut, Beirut) to protest against Israel and in support of Palestine. ---- On 25 May 2024, university students took to the streets in front of the American University of Beirut in Bliss Street in Beirut - Ras Beirut (Beirut, Beirut) to protest against the continuous Israeli bombardment of Gaza. They rallied in support of the Palestinian people. ---- On 27 May 2024, contracted teachers staged a protest in front the Lebanese University in Beirut - Mazraa (Beirut, Beirut) due to low wages and poor working conditions. ---- On 28 May 2024, contracted teachers staged a protest in front of the Grand Serail in Beirut - Minet El Hosn (Beirut, Beirut) due to low wages and poor working conditions. ---- On 20 June 2024, groups of students took to the streets in front of the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut) to protest against the continuation of official exams for students in the south, despite the ongoing cross-border exchanges between Israel and Hezbollah. ---- On 24 July 2024, the official committee of hourly contract professors at the Lebanese University carried out a sit-in in front of the Ministry of Education and Higher Education at UNESCO in Beirut - Mousseitbeh (Beirut, Beirut) to demand the government and the university's administration respect their labor rights. ---- On 5 February 2025, Palestinian refugees shut down UNRWA centers, and offices in Beirut - Mousseitbeh (Beirut, Beirut) by refusing to work and blocked entrances.. The shut down was in demonstration against the 'arbitrary' suspension of five teachers since October 2024. ---- On 24 March 2025, the Public Schools Teachers Association staged a sit-in outside the Ministry of Education headquarters in Beirut - Mousseitbeh (Beirut, Beirut). The protest followed a two-day warning strike in response to a ministerial decision to withhold productivity compensation during the summer. ---- On 26 March 2025, public primary school teachers took to the streets in front of the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut) to demand the government to disperse their outstanding financial dues. The Public Teachers Association called for the protest. ---- On 7 April 2025, employees and teachers of the Lebanese University carried out a protest in front of the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut) to demand ''equal rights with public sector employees and to receive their salaries with the increments approved by the government.'' ---- On 7 April 2025, university students took to the streets in front of the AUB main gate in Beirut - Ras Beirut (Beirut, Beirut) to protest against Israeli attacks against Gaza. They rallied in support of the Palestinian people. LAU university students also carried out a protest in the Qoreitem area with the same demands. ---- On 17 April 2025, public school teachers took to the streets in front of the TVA building in Beirut - Achrafieh (Beirut, Beirut) to protest against the government's decision to deprive them of their monthly summer productivity allowance, which accounts to USD 375. The Public Teachers School Association called for the protest. This comes after teachers protested the same day in front of the Ministry of Education building near UNESCO. ---- On 17 April 2025, public school teachers took to the streets in front of the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut) to protest against the government's decision to deprive them of their monthly summer productivity allowance, which accounts to USD 375. The Public Teachers School Association called for the protest. ---- On 24 April 2025, more than 2,000 teachers took to the streets in front of the Ministry of Education building in Beirut - Mousseitbeh (Beirut, Beirut) to demand higher wages and better working conditions. The Public Schools Teachers Association called for the protest. ---- On 24 April 2025, following the protest in front of the Ministry of Education, more than 2000 teachers rallied near the National Parliament in Beirut - Port (Beirut, Beirut) to demand higher wages and better working conditions. The protest took place during a parliamentary session. The Public Schools Teachers Association called for the protest. ---- On 2 May 2025, high school students held a protest sit-in in front of the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut) to demand the inclusion of optional subjects in official exams and a reduction in the curriculum. ---- On 9 May 2025, high school students took to the streets in front of the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut) to protest against the new minister's policies regarding official exams. ---- On 11 May 2025, several hundred of high school students protested outside the Ministry of Education in Beirut - Mousseitbeh (Beirut, Beirut), opposing policies introduced by Minister Rima Karami. The students called on the minister to ease her stance on the Lebanese baccalaureate exams scheduled for 9 July. ---- On 27 June 2025, protesters took to the streets in front of the United Nations Relief and Works Agency in Beirut - Mousseitbeh (Beirut, Beirut) to protest against the agency's decision to expel four Palestinian teachers. The Public Teachers Association called for the protest. Protesters also rallied in support of Gaza. ---- On 30 June 2025, contract teachers in public schools took to the streets in front of the National Parliament in Beirut - Port (Beirut, Beirut) to call for better wages and working conditions. The protest coincided with a parliamentary session. ---- On 8 July 2025, contractual public school teachers staged a protest in front of the Grand Serail in Beirut - Minet el Hosn (Beirut, Beirut), demanding better wages and improved working conditions from the government.</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>2024-10-15 ---- 2024-10-23 ---- 2025-03-10 ---- 2025-04-09 ---- 2025-07-05</t>
+          <t>2024-01-16 ---- 2024-02-20 ---- 2024-03-05 ---- 2024-03-15 ---- 2024-03-28 ---- 2024-04-30 ---- 2024-04-30 ---- 2024-04-30 ---- 2024-04-30 ---- 2024-04-30 ---- 2024-05-07 ---- 2024-05-13 ---- 2024-05-15 ---- 2024-05-15 ---- 2024-05-23 ---- 2024-05-25 ---- 2024-05-27 ---- 2024-05-28 ---- 2024-06-20 ---- 2024-07-24 ---- 2025-02-05 ---- 2025-03-24 ---- 2025-03-26 ---- 2025-04-07 ---- 2025-04-07 ---- 2025-04-17 ---- 2025-04-17 ---- 2025-04-24 ---- 2025-04-24 ---- 2025-05-02 ---- 2025-05-09 ---- 2025-05-11 ---- 2025-06-27 ---- 2025-06-30 ---- 2025-07-08</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Bint Jbeil</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -805,11 +739,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LB43</t>
+          <t>LB21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -824,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -857,41 +791,41 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2025-03-28 ---- 2025-02-17 ---- 2024-01-22</t>
+          <t>2024-09-25</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>March 2025: An educational facility was set alight when Israeli forces fired artillery and white phosphorus shells. ---- February 2025: The vicinity of an educational facility was bombed by an Israeli drone as part of a wider attack on the area during a ceasefire. ---- January 2024: An educational facility was damaged by Israeli airstrikes.</t>
+          <t xml:space="preserve">September 2024: A UN school sustained minor damage, including broken windows from nearby Israeli airstrike blasts. Repairs were underway. </t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building </t>
+          <t xml:space="preserve">Education Building </t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Foreign Forces - Military ---- Foreign Forces - Military ---- Foreign Forces - Military</t>
+          <t>Foreign Forces - Military</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Israeli Defence Forces ---- Israeli Defence Forces ---- Israeli Defence Forces</t>
+          <t>Israeli Defence Forces</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Artillery ---- Aerial Bomb: Drone ---- Aerial Bomb: Plane</t>
+          <t>Aerial Bomb: Plane</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
+          <t>School: No Further Details</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -899,60 +833,60 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Al Nabatieh</t>
+          <t>Baalbek-Hermel</t>
         </is>
       </c>
       <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>6</v>
       </c>
-      <c r="AE3" t="n">
-        <v>8</v>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>LB4</t>
+          <t>LB8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Strategic developments ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+          <t>Protests ---- Explosions/Remote violence ---- Protests ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Looting/property destruction ---- Air/drone strike ---- Shelling/artillery/missile attack</t>
+          <t>Peaceful protest ---- Air/drone strike ---- Peaceful protest ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr"/>
+          <t>Protesters (Lebanon) ---- Military Forces of Israel (2022-) ---- Protesters (Lebanon) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Teachers (Lebanon) ---- Students (Lebanon)</t>
+        </is>
+      </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Hezbollah ---- Civilians (Lebanon) ---- Civilians (Lebanon) ---- Civilians (Lebanon) ---- Civilians (Lebanon)</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Police Forces of Lebanon (2021-)</t>
-        </is>
-      </c>
+          <t>Hezbollah</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>On 7 April 2024, an Israeli drone fired missiles targeting several areas in Houla town (Marjayoun, Al Nabatieh) amid ongoing hostilities with Hezbollah. The Israeli military also fired artillery shells near the town's school. There were no casualties. ---- On 23 June 2024, Israeli warplanes carried out an airstrike in Khiyam town (Marjayoun, Al Nabatieh) amid ongoing hostilities with Hezbollah. The Israeli military also fired artillery and white phosphorus shells near Al Mabbarat school, and Al Shalihat area. There were no casualties. The Israeli military announced it had struck military infrastructure for Hezbollah in the town. International organizations have accused Israel of using white phosphorous bombs during the current war between Hezbollah and Israel. ---- On 6 October 2024, Israeli warplanes and drones carried out two airstrikes at the entrance of the city and near Ain al-Saghira, on Jdeidet Marjeyoun, in Marjayoun (Marjayoun, Al Nabatieh). 3 people were killed and 3 others were injured. One victim was a man and a sergeant of the Internal Security Forces, another was a female teacher. This event is part of the Israeli army's announcement of intensified bombing in Lebanon, including in the north, where it claimed to have pushed back Hezbollah, as part of the 'new phase' of Israel's war on Gaza, in the midst of hostilities against Hezbollah. ---- On 15 October 2024, Israeli warplanes carried out two airstrikes, including one around the Al Mabrat school, in Khiyam (Marjayoun, Al Nabatieh). One person was killed. The Israeli military also fired artillery shells. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 19 October 2024, Israeli warplanes carried out an airstrike on the Imam Musa al Sadr Intermediate School in Qabrikha (Marjayoun, Al Nabatieh). Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- Property destruction: On 19 October 2024, overnight, the Israeli army blew up residential buildings in a neighborhood in Mays el Jabal (Marjayoun, Al Nabatieh). A school was destroyed. There were no casualties. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 23 December 2024, Israeli warplanes carried out an airstrike targeting an area near a school in Taybeh town and an Israeli drone (Marjayoun, Al Nabatieh). Two people were killed and another was injured in the airstrike. This event occurred following the implementation of the ceasefire agreement on 27 November. ---- On 28 March 2025, the Israeli military fired artillery and white phosphorus shells towards Khiyam town (Marjayoun, Al Nabatieh). A fire broke out in a public school in Al Baraka neighborhood due to the shelling. There were no casualties. HRW and other international organizations have accused Israel of using white phosphorous bombs in this attack.</t>
+          <t>On 26 February 2024, town residents, mukhtars, municipality council members, teachers and activists marched across Bednayel (Baalbek-Hermel, Baalbek) to protest against the increase in crime. They blocked the main road of the town by standing on the road. ---- On 11 March 2024, Israeli warplanes carried out an airstrike near Al Mahdi school in Chmistar (Baalbek, Baalbek-Hermel) amid ongoing hostilities with Hezbollah. There were no casualties. ---- On 7 May 2024, university students protested at the Lebanese University in Douris (Baalbek, Baalbek-Hermel) in support of Palestine and Gaza. They rallied against the continuous Israeli bombardment of Gaza. ---- On 25 September 2024, Israeli airplanes carried out airstrikes in Baalbek (Baalbek, Baalbek-Hermel). Al-Salah Islamic High School was damaged. Casualties unknown. The Israeli army announced it had targeted around 280 Hezbollah sites throughout the day. This event is part of what the Israeli army called the 'new phase' of its war on Gaza, which has targeted several cities in Lebanon amid ongoing hostilities against Hezbollah. ---- On 6 October 2024, Israeli warplanes carried out an airstrike and targeted a building at the southern entrance of the city, towards the Al-Wad residential neighborhood, near the National Maronite School, in Baalbek (Baalbek, Baalbek-Hermel). Casualties unknown. This event is part of the Israeli army's announcement of intensified bombing in Lebanon, including in the north where it claimed to have pushed back Hezbollah, as part of the 'new phase' of Israel's war on Gaza, in the midst of hostilities against Hezbollah. ---- On 14 October 2024, Israeli warplanes carried out an airstrike behind the Al Bashaer High School, on the side of Ain Bourday (Baalbek, Baalbek-Hermel). Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>2024-04-07 ---- 2024-06-23 ---- 2024-10-06 ---- 2024-10-15 ---- 2024-10-19 ---- 2024-10-19 ---- 2024-12-23 ---- 2025-03-28</t>
+          <t>2024-02-26 ---- 2024-03-11 ---- 2024-05-07 ---- 2024-09-25 ---- 2024-10-06 ---- 2024-10-14</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Marjayoun</t>
+          <t>Baalbek</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -962,11 +896,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LB63</t>
+          <t>LB22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -981,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1014,41 +948,41 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2025-05-13 ---- 2024-11-07 ---- 2024-10-09</t>
+          <t>2025-02-09</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>May 2025: An education facility was hit when an Israeli drone dropped a stun grenade over it. ---- November 2024: The vicinity of an educational facility was hit by Israeli airstrikes. ---- October 2024: An educational centre of a LNGO was heavily damaged during an attack by suspected Israeli forces on a neighbouring health centre. The centre was providing psychological support and education for over 400 children and is currently not operational due to the damage.</t>
+          <t>February 2025: An educational facility was shelled by Syrian military and HTS artillery.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building </t>
+          <t xml:space="preserve">Education Building </t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Foreign Forces - Military ---- Foreign Forces - Military ---- Foreign Forces - Military</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Israeli Defence Forces ---- Israeli Defence Forces ---- Israeli Defence Forces</t>
+          <t>Syrian Armed Forces, Tahrir al-Sham</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Tasers, Live and Rubber Bullets ---- Aerial Bomb: Plane ---- Aerial Bomb: No Information on Platform Type</t>
+          <t>Artillery</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
+          <t>School: No Further Details</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -1056,60 +990,56 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Baalbek-Hermel</t>
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>LB6</t>
+          <t>LB8</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Strategic developments ---- Strategic developments</t>
+          <t>Explosions/Remote violence ---- Protests</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Other ---- Other</t>
+          <t>Shelling/artillery/missile attack ---- Peaceful protest</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Hezbollah ---- Protesters (Palestine) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
+          <t>Military Forces of Syria (2024-) ---- Protesters (Lebanon)</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Refugees/IDPs (Palestine)</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Civilians (Lebanon) ---- Military Forces of Israel (2022-)</t>
-        </is>
-      </c>
+          <t>Teachers (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>On 4 October 2024, Israeli warplanes carried out an airstrike targeting an area near the public school in a village on the outskirts of Burj Rahhal town (Tyr, South) amid ongoing hostilities with Hezbollah. Casualties unknown. ---- On 2 November 2024, overnight until the morning, Israeli warplanes carried out airstrikes on buildings and apartments near the Imam Hussein complex in Tyr (Tyr, South). The buildings were completely destroyed. The Israeli army also fired artillery shells. 9 people were killed and 12 others were injured. It also caused serious damage to buildings, residential neighborhoods, infrastructures, streets, electricity, water and telephone networks. A fire broke out twice near the Evangelical School. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 11 November 2024, overnight and until the morning, Israeli warplanes carried out airstrikes on the Ain Al Tutah neighborhood between Burj Rahhal and Aabbassiye (Tyr, South). They also targeted the Qastal School junction, in the Aabbassiye junction. Shops for household electrical equipment were targeted. Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 24 November 2024, Hezbollah militants fired a guided missile on an Israeli Merkava tank near a school in Jebbayn (Tyr, South). Casualties Unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 19 December 2024, Palestinian refugees protested in front of the 'Palestine' school in Burj Shemali (Tyr, South) after UNRWA announced the closure of the school. UNRWA also announced that students will be moved to 'Jabalia' school in the refugee camp. ---- Other: On 13 May 2025, an Israeli drone dropped a stun grenade over a school in Ed Dhayra town (Tyr, South). ---- Other: On 15 May 2025, an Israeli drone dropped a stun grenade over a destroyed school in Ed Dhayra town (Tyr, South). There were no casualties.</t>
+          <t>On 9 February 2025, Syrian forces from the post-Assad regime fired artillery shells struck Qanafez town (Al Hermel, Baalbek-Hermel). The shelling targeted a school in the town. There were no casualties. This took place amid confrontations between Syrian forces and Lebanese clans, including Jaafar and Zaiter, engaged in smuggling operations for Hezbollah. ---- On 30 April 2025, public school teachers held a protest in front of the city's serail in Al Hermel city (Al Hermel, Baalbek-Hermel). The protest was directed against Education Minister Rima Karameh, with protesters accusing her of neglecting their right to social assistance.</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2024-10-04 ---- 2024-11-02 ---- 2024-11-11 ---- 2024-11-24 ---- 2024-12-19 ---- 2025-05-13 ---- 2025-05-15</t>
+          <t>2025-02-09 ---- 2025-04-30</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Tyr</t>
+          <t>Al Hermel</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -1119,154 +1049,88 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LB21</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2024-09-25</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">September 2024: A UN school sustained minor damage, including broken windows from nearby Israeli airstrike blasts. Repairs were underway. </t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Foreign Forces - Military</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Israeli Defence Forces</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Aerial Bomb: Plane</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>LB23</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Baalbek-Hermel</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>LB8</t>
+          <t>LB2</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Protests ---- Explosions/Remote violence ---- Protests ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+          <t>Explosions/Remote violence</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Air/drone strike ---- Peaceful protest ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike</t>
+          <t>Air/drone strike</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Protesters (Lebanon) ---- Military Forces of Israel (2022-) ---- Protesters (Lebanon) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Teachers (Lebanon) ---- Students (Lebanon)</t>
-        </is>
-      </c>
+          <t>Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Hezbollah</t>
+          <t>Civilians (Lebanon)</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>On 26 February 2024, town residents, mukhtars, municipality council members, teachers and activists marched across Bednayel (Baalbek-Hermel, Baalbek) to protest against the increase in crime. They blocked the main road of the town by standing on the road. ---- On 11 March 2024, Israeli warplanes carried out an airstrike near Al Mahdi school in Chmistar (Baalbek, Baalbek-Hermel) amid ongoing hostilities with Hezbollah. There were no casualties. ---- On 7 May 2024, university students protested at the Lebanese University in Douris (Baalbek, Baalbek-Hermel) in support of Palestine and Gaza. They rallied against the continuous Israeli bombardment of Gaza. ---- On 25 September 2024, Israeli airplanes carried out airstrikes in Baalbek (Baalbek, Baalbek-Hermel). Al-Salah Islamic High School was damaged. Casualties unknown. The Israeli army announced it had targeted around 280 Hezbollah sites throughout the day. This event is part of what the Israeli army called the 'new phase' of its war on Gaza, which has targeted several cities in Lebanon amid ongoing hostilities against Hezbollah. ---- On 6 October 2024, Israeli warplanes carried out an airstrike and targeted a building at the southern entrance of the city, towards the Al-Wad residential neighborhood, near the National Maronite School, in Baalbek (Baalbek, Baalbek-Hermel). Casualties unknown. This event is part of the Israeli army's announcement of intensified bombing in Lebanon, including in the north where it claimed to have pushed back Hezbollah, as part of the 'new phase' of Israel's war on Gaza, in the midst of hostilities against Hezbollah. ---- On 14 October 2024, Israeli warplanes carried out an airstrike behind the Al Bashaer High School, on the side of Ain Bourday (Baalbek, Baalbek-Hermel). Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah.</t>
+          <t>On 5 October 2024, at dawn, Israeli airplanes carried out an airstrike in Rafid (Rashayya, Bekaa) targeting the house of the director of Al-Abrar school and killing his mother. This event is part of the Israeli army's announcement of intensified bombing in Lebanon, including in the north, where it claimed to have pushed back Hezbollah, as part of the 'new phase' of Israel's war on Gaza, in the midst of hostilities against Hezbollah.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2024-02-26 ---- 2024-03-11 ---- 2024-05-07 ---- 2024-09-25 ---- 2024-10-06 ---- 2024-10-14</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Baalbek</t>
+          <t>Rashayya</t>
         </is>
       </c>
       <c r="AQ5" t="n">
@@ -1276,153 +1140,1783 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LB22</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2025-02-09</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>February 2025: An educational facility was shelled by Syrian military and HTS artillery.</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Education Building </t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Syrian Armed Forces, Tahrir al-Sham</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Artillery</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>School: No Further Details</t>
-        </is>
-      </c>
+          <t>LB24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Baalbek-Hermel</t>
+          <t>Bekaa</t>
         </is>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>LB8</t>
+          <t>LB2</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Explosions/Remote violence ---- Protests</t>
+          <t>Protests</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Shelling/artillery/missile attack ---- Peaceful protest</t>
+          <t>Peaceful protest</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Military Forces of Syria (2024-) ---- Protesters (Lebanon)</t>
+          <t>Protesters (Lebanon)</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Teachers (Lebanon)</t>
+          <t>Students (Lebanon)</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>On 9 February 2025, Syrian forces from the post-Assad regime fired artillery shells struck Qanafez town (Al Hermel, Baalbek-Hermel). The shelling targeted a school in the town. There were no casualties. This took place amid confrontations between Syrian forces and Lebanese clans, including Jaafar and Zaiter, engaged in smuggling operations for Hezbollah. ---- On 30 April 2025, public school teachers held a protest in front of the city's serail in Al Hermel city (Al Hermel, Baalbek-Hermel). The protest was directed against Education Minister Rima Karameh, with protesters accusing her of neglecting their right to social assistance.</t>
+          <t>On 30 April 2024, university students protested at the LIU campus in Houch el Harime (West Bekaa, Bekaa) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people.</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2025-02-09 ---- 2025-04-30</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Al Hermel</t>
+          <t>West Bekaa</t>
         </is>
       </c>
       <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LB25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bekaa</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>LB2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Students (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>On 30 April 2024, university students protested at the BAU campus in Taalabaya (Zahle, Bekaa) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Zahle</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LB32</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mount Lebanon</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>LB3</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests ---- Protests ---- Explosions/Remote violence ---- Riots ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Air/drone strike ---- Mob violence ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon) ---- Protesters (Palestine) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Military Forces of Israel (2022-) ---- Rioters (Lebanon) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Students (Lebanon); Teachers (Lebanon) ---- Aid Workers (Lebanon); Protesters (Lebanon); Students (Lebanon); Students (Palestine); Teachers (Lebanon); Teachers (Palestine); Teachers Syndicate; UNRWA: United Nations Relief and Works Agency ---- Students (Lebanon) ---- Students (Lebanon) ---- Hezbollah ---- Students (Lebanon); Teachers (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Civilians (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>On 9 April 2024, teachers and students gathered in Al Hikme University in Furn el Chebbak (Baabda, Mount Lebanon) to condemn the killing of LF Official Pascale Sleiman. They also held the gathering in support of his family. ---- On 18 April 2024, Palestinian and Lebanese students, teachers, as well as members of the Teachers Syndicate took to the streets in front of the UNRWA building in Bir Hasan (Baabda, Mount Lebanon) to protest against the latest rules implemented by the agency against its employees. Protesters also rallied in support of Gaza and the Palestinian people. ---- On 30 April 2024, university students protested at the LU campus in Laylaki (Baabda, Mount Lebanon) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. ---- On 23 May 2024, university students took to the streets in front of the Egyptian embassy in Bir Hasan (Baabda, Mount Lebanon) to protest against Israel and in support of Palestine. ---- On 16 October 2024, Israeli warplanes carried out three airstrikes in Haret Hreik (Baabda, Mount Lebanon), including on a building next to the Qaayq school. Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 23 December 2024, a group of rioters (affiliated with Hezbollah) opened fire, vandalized, and broke the external and internal gates of the Saint George school in Haret Hreik (Baabda, Mount Lebanon). The incident followed the circulation of a controversial video allegedly insulting Hezbollah Secretary-General Sayyed Hassan Nasrallah, featuring Lebanese Singer Ragheb Alama's voice. ---- On 17 May 2025, teachers, students, and parents held a protest in front of the main gate of Al Rusol School in Salima (Baabda, Mount Lebanon) against the administration's decision to close the school before the end of the academic year, following recent tuition fee increases.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>2024-04-09 ---- 2024-04-18 ---- 2024-04-30 ---- 2024-05-23 ---- 2024-10-16 ---- 2024-12-23 ---- 2025-05-17</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Baabda</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LB33</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mount Lebanon</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>LB3</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Students (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>On 30 April 2024, university students protested at the BAU campus in Debbieh (Chouf, Mount Lebanon) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. ---- On 21 June 2025, parents of students gathered and temporarily blocked the road in front of a public high school in Aanout town (Chouf, Mount Lebanon) to protest against the Ministry of Education's decision of closing the English department in the school.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>2024-04-30 ---- 2025-06-21</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Chouf</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LB34</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mount Lebanon</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>LB3</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>FPM: Free Patriotic Movement ---- FPM: Free Patriotic Movement</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>On 16 April 2024, FPM supporters took to the streets in front of a state school in Aamchit city (Jubayl, Mount Lebanon) to protest against the afternoon teaching of Syrian refugees at the school. The FPM called for the protest. ---- On 16 April 2024, FPM supporters took to the streets in front of a state school in Jbeil city (Jubayl, Mount Lebanon) to protest against the afternoon teaching of Syrian refugees at the school. The FPM called for the protest.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>2024-04-16 ---- 2024-04-16</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Jubayl</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LB35</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mount Lebanon</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>LB3</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Protests</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Students (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>On 30 April 2024, university students protested at the Holy Spirit university campus in Sarba (Keserwan, Mount Lebanon) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people.</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Keserwan</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LB36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mount Lebanon</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>LB3</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Lebanese Forces ---- Students (Lebanon); Tashnag Party; Zavarian Student Association</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>On 17 September 2024, members of the Lebanese Forces took to the streets in front of the General Directorate for Professional and Technical Education in Ed Dekouane (Al Matn, Mount Lebanon) against the Ministry of Education's decisions regarding Syrian students. ---- On 26 April 2025, students held a protest in front of the Turkish Embassy in Rabieh (Al Matn, Mount Lebanon) to denounce Turkey's ongoing denial of the Armenian genocide. The protest was organized by the Zavarian Student Association, affiliated with the Tashnag Party.</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>2024-09-17 ---- 2025-04-26</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Al Matn</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LB41</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">October 2024: An educational facility was destroyed by Israeli airstrikes. </t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Foreign Forces - Military</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Israeli Defence Forces</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aerial Bomb: Plane</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Al Nabatieh</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>LB4</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Battles ---- Violence against civilians ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Armed clash ---- Attack ---- Air/drone strike ---- Air/drone strike</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Military Forces of Israel (2022-) ---- Hezbollah ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Military Forces of Israel (2022-) ---- Civilians (Lebanon) ---- Hezbollah</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Lebanon) ---- Civilians (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>On 15 October 2024, Israeli warplanes carried out an airstrike on a house near a school in Qalaouiye (Bint Jbeil, Al Nabatieh). The house was destroyed. Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 23 October 2024, Hezbollah fired several missiles targeting an Israeli infantry force near a school in Ramieh town (Bint Jbeil, Al Nabatieh). The Israeli military also fired artillery shells towards the town. The group announced it had achieved direct hits. IDF announced that during the clashes in Southern Lebanon on the day, 4 soldiers from the 2nd Carmeli Reserve Infantry Brigade were killed, which is coded to this location. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 10 March 2025, several Israeli soldiers moved to the entrance of Ramieh (Bint Jbeil, Al Nabatieh) and opened fire toward a local school, which had been converted into a service center following the war between Hezbollah and Israel. A group of individuals (likely displaced families) managed to escape unharmed. There were no casualties. ---- On 9 April 2025, an Israeli drone struck an area with a missile near a public school in Ramieh town (Bint Jbeil, Al Nabatieh). There were no casualties. ---- On 5 July 2025, an Israeli drone struck a car with a missile in Bent Jbeil city (Bint Jbeil, Al Nabatieh). A second Israeli drone targeted a van near the vocational school in the city. One individual was killed and two others were injured in the attack. The Israeli Defense Forces (IDF) claimed that the deceased was a member of Hezbollah's elite Radwan Force unit.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>2024-10-15 ---- 2024-10-23 ---- 2025-03-10 ---- 2025-04-09 ---- 2025-07-05</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Bint Jbeil</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LB42</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Al Nabatieh</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>LB4</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Air/drone strike</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Civilians (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>On 17 February 2025, an Israeli drone dropped bombs near a local school in Kfar Chouba town (Hasbeiya, Al Nabatieh). Also, an Israeli mechanized force combed with machine gunfire and threw hand grenades towards the town's center and Al Sawwan neighborhood in the town. There were no casualties. This event occurred following the extension of the ceasefire agreement until 18 February.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Hasbeiya</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LB43</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>3</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2025-03-28 ---- 2025-02-17 ---- 2024-01-22</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>March 2025: An educational facility was set alight when Israeli forces fired artillery and white phosphorus shells. ---- February 2025: The vicinity of an educational facility was bombed by an Israeli drone as part of a wider attack on the area during a ceasefire. ---- January 2024: An educational facility was damaged by Israeli airstrikes.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Foreign Forces - Military ---- Foreign Forces - Military ---- Foreign Forces - Military</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Israeli Defence Forces ---- Israeli Defence Forces ---- Israeli Defence Forces</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Artillery ---- Aerial Bomb: Drone ---- Aerial Bomb: Plane</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Al Nabatieh</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>LB4</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Strategic developments ---- Explosions/Remote violence ---- Explosions/Remote violence</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Looting/property destruction ---- Air/drone strike ---- Shelling/artillery/missile attack</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Hezbollah ---- Civilians (Lebanon) ---- Civilians (Lebanon) ---- Civilians (Lebanon) ---- Civilians (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Police Forces of Lebanon (2021-)</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>On 7 April 2024, an Israeli drone fired missiles targeting several areas in Houla town (Marjayoun, Al Nabatieh) amid ongoing hostilities with Hezbollah. The Israeli military also fired artillery shells near the town's school. There were no casualties. ---- On 23 June 2024, Israeli warplanes carried out an airstrike in Khiyam town (Marjayoun, Al Nabatieh) amid ongoing hostilities with Hezbollah. The Israeli military also fired artillery and white phosphorus shells near Al Mabbarat school, and Al Shalihat area. There were no casualties. The Israeli military announced it had struck military infrastructure for Hezbollah in the town. International organizations have accused Israel of using white phosphorous bombs during the current war between Hezbollah and Israel. ---- On 6 October 2024, Israeli warplanes and drones carried out two airstrikes at the entrance of the city and near Ain al-Saghira, on Jdeidet Marjeyoun, in Marjayoun (Marjayoun, Al Nabatieh). 3 people were killed and 3 others were injured. One victim was a man and a sergeant of the Internal Security Forces, another was a female teacher. This event is part of the Israeli army's announcement of intensified bombing in Lebanon, including in the north, where it claimed to have pushed back Hezbollah, as part of the 'new phase' of Israel's war on Gaza, in the midst of hostilities against Hezbollah. ---- On 15 October 2024, Israeli warplanes carried out two airstrikes, including one around the Al Mabrat school, in Khiyam (Marjayoun, Al Nabatieh). One person was killed. The Israeli military also fired artillery shells. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 19 October 2024, Israeli warplanes carried out an airstrike on the Imam Musa al Sadr Intermediate School in Qabrikha (Marjayoun, Al Nabatieh). Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- Property destruction: On 19 October 2024, overnight, the Israeli army blew up residential buildings in a neighborhood in Mays el Jabal (Marjayoun, Al Nabatieh). A school was destroyed. There were no casualties. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 23 December 2024, Israeli warplanes carried out an airstrike targeting an area near a school in Taybeh town and an Israeli drone (Marjayoun, Al Nabatieh). Two people were killed and another was injured in the airstrike. This event occurred following the implementation of the ceasefire agreement on 27 November. ---- On 28 March 2025, the Israeli military fired artillery and white phosphorus shells towards Khiyam town (Marjayoun, Al Nabatieh). A fire broke out in a public school in Al Baraka neighborhood due to the shelling. There were no casualties. HRW and other international organizations have accused Israel of using white phosphorous bombs in this attack.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>2024-04-07 ---- 2024-06-23 ---- 2024-10-06 ---- 2024-10-15 ---- 2024-10-19 ---- 2024-10-19 ---- 2024-12-23 ---- 2025-03-28</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Marjayoun</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LB44</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Al Nabatieh</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>LB4</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Air/drone strike ---- Peaceful protest ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Protesters (Lebanon) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Students (Lebanon); Teachers (Lebanon) ---- Hezbollah; Students (Lebanon); Teachers (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Hezbollah ---- Hezbollah ---- Civilians (Lebanon) ---- Civilians (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Civilians (Lebanon) ---- Civilians (Lebanon); Students (Lebanon) ---- Health Workers (Lebanon); Hezbollah; Islamic Health Society</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>On 14 February 2024, Israeli warplanes carried out an airstrike on the Maslakh neighborhood in Nabatiye town (Al Nabatieh, Al Nabatieh). An Israeli drone also targeted an apartment near the Sabbah High School in the city. This comes as cross-border exchanges continue with Hezbollah. Three Hezbollah members, and eight civilians were killed and two individuals were injured in the airstrikes. ---- On 23 May 2024, an Israeli drone struck a car along a main road in Kfar Dajjal town (Al Nabatieh, Al Nabatieh). One Hezbollah member was killed in the attack. Three school students were also injured in the attack in a nearby van in the area. ---- On 23 May 2024, students and teachers organized a protest at the Hassan Kamel Al Sabbah school in Nabatiye city (Al Nabatieh, Al Nabatieh) against Israeli bombardment of south Lebanon. This came after an Israeli drone struck a car and killed a teacher and Hezbollah member near the city. ---- On 11 October 2024, Israeli warplanes carried out several airstrikes in Nabatiye (Al Nabatieh, Al Nabatieh), including one close to the Soeurs Antonines high school. Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 14 October 2024, Israeli warplanes carried out a series of airstrikes in the eastern neighborhood in Yohmor al Shaqif (Al Nabatieh, Al Nabatieh). In the afternoon, the Islamic Health Authority Center was also destroyed by an airstrike. It caused an unspecified number of fatalities coded to 3. Five other houses were destroyed. An airstrike targeted the vicinity of a school and cut off the city's main road. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 2 November 2024, Israeli warplanes carried out an airstrike near a secondary school in Mayfadoun (Al Nabatieh, Al Nabatieh). Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 7 November 2024, Israeli warplanes carried out an airstrike targeting an area near the local school in Zebdine town (Al Nabatieh, Al Nabatieh). Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 12 November 2024, at around 4:10 pm, Israeli warplanes carried out an airstrike targeting the vicinity of the International School in Habbouch (Al Nabatieh, Al Nabatieh). Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 22 November 2024, Israeli drone carried out a strike with a guided missile targeting a motorcycle on the road in Nabatiyeh El Faouqa (Al Nabatieh, Al Nabatieh), near Sabah Al Zamiyyah high school. An individual was killed. 1 fatality. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 11 April 2025, teachers, students, and Hezbollah supporters took to the streets in Nabatiye city (Al Nabatieh, Al Nabatieh) to protest against the Israeli bombardment of Gaza. They rallied in support of the Palestinian people.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>2024-02-14 ---- 2024-05-23 ---- 2024-05-23 ---- 2024-10-11 ---- 2024-10-14 ---- 2024-11-02 ---- 2024-11-07 ---- 2024-11-12 ---- 2024-11-22 ---- 2025-04-11</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Al Nabatieh</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LB51</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Akkar</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>LB7</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon) ---- Protesters (Palestine)</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Palestine)</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>On 3 September 2024, parents of students at Al Bireh high school staged a sit-in infront of the school in El Bire (Akkar, Akkar) to protest the increase in fees imposed by the Ministry of Education. ---- On 5 February 2025, Palestinian refugees shut down UNRWA centers, offices and schools in Nahr el Bared camp (Akkar, Akkar) by refusing to work and blocked entrances. The shut down was in demonstration against the 'arbitrary' suspension of five teachers since October 2024.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>2024-09-03 ---- 2025-02-05</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Akkar</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LB55</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>LB5</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Riots ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Mob violence ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Rioters (Lebanon) ---- Protesters (Palestine)</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Palestine)</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>On 5 June 2024, a group of rioters set flames to a school in Bhannine (Al Miniyeh Al Danniyeh, North) due to a dispute. There were no casualties. ---- On 5 February 2025, Palestinian refugees shut down UNRWA centers, offices and schools in Beddawi camp (Al Miniyeh al Danniyeh, North) by refusing to work and blocked entrances.. The shut down was in demonstration against the 'arbitrary' suspension of five teachers since October 2024.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>2024-06-05 ---- 2025-02-05</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Al Miniyeh Al Danniyeh</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LB56</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>LB5</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Students (Lebanon); Teachers (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon) ---- Students (Lebanon); Teachers (Lebanon) ---- FENASOL: National Federation of Workers' and Employees' Trade Unions; Labor Group (Lebanon); Teachers (Lebanon); Teachers Syndicate</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>On 4 January 2024, protesters including students, teachers and parents held a sit-in outside the Education Department in Tripoli (Tripoli), in protest against the closing of a 'Tawjeeh' school. ---- On 30 April 2024, university students protested at the BAU campus in El Mina (Tripoli, North) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. ---- On 25 April 2025, a group of students temporarily blocked the road during a protest in front of the Ministry of Education building in Tripoli (Tripoli, North). They called upon the ministry to change the education system. ---- On 28 April 2025, students and teachers of George Sarraf High School held a protest sit-in in the school courtyard in Abi Samra (Tripoli, North) to denounce the widespread presence of uncontrolled firearms in the city. The protest followed the accidental killing of a student during a dispute at the Abi Samra roundabout. Protesters called on the state and security forces to address the deteriorating security situation in the area. ---- On 20 May 2025, several workers and employees briefly blocked the street in front of the Serail in Tripoli city (Tripoli, North) to protest what they described as government 'procrastination.' The demonstration was organized in response to a call by FENASOL and supported by various unions, including the Syndicate of Tripoli Municipality Workers, the Syndicate of Mina Municipality Workers, the Oil Installations and Refinery Workers' Unions, the Syndicate of Kadisha Electricity Workers and Employees, and the North Teachers' Syndicate.</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>2024-01-04 ---- 2024-04-30 ---- 2025-04-25 ---- 2025-04-28 ---- 2025-05-20</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Tripoli</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LB61</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>LB6</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests ---- Protests ---- Riots ---- Protests</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Mob violence ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Protesters (Lebanon) ---- Protesters (Lebanon) ---- Protesters (Palestine) ---- Protesters (Lebanon) ---- Rioters (Lebanon) ---- Protesters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Hezbollah; Students (Lebanon) ---- Students (Lebanon); Teachers (Lebanon) ---- Refugees/IDPs (Palestine) ---- Labor Group (Lebanon); Public Schools Teachers Association; Teachers (Lebanon) ---- Muslim Group (Lebanon); Students (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Rioters (Lebanon)</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>On 30 April 2024, university students protested at the Faculty of Law-Lebanese University in Sidon (Sayda, South) against the Israeli bombardment of Gaza. Students rallied in support of Gaza and the Palestinian people. Hezbollah called for the rally. ---- On 23 May 2024, students and teachers organized a sit-in at a school in Sidon (Sayda, South) in support of the children injured by an Israeli airstrike in Kfar Dajjal. ---- On 5 February 2025, Palestinian refugees shut down the U.N. agency for Palestinian Refugees (UNRWA) centers, offices and schools in Ein el Hilweh camp (Sayda, South) by refusing to work and blocked entrances. The shut down was in demonstration against the 'arbitrary' suspension of five teachers since October 2024. ---- On 14 April 2025, teachers and administrative staff of the Omani Public School in Sidon city (Sayda, South) organized a protest in front of the school entrance. The protest was held in objection to the delay in payment of their dues and the low wages they receive. The participants also affirmed their support for the demands of the public education unions in Lebanon, including the Public Teachers Association. ---- On 24 May 2025, a brawl took place between two opposing political candidate lists in front of the Kuwaiti School in Sidon city (Sayda, South). A separate altercation occurred the same day outside the Maarouf Saad Cultural Center in the city. ---- On 20 July 2025, various groups, including scouting movements, mosque committees, institutional organizations, medical associations, student unions, and neighborhood committees, organized a protest sit-in in Sidon city (Sayda, South) to demand an end to Israeli bombardment of Gaza. The protesters expressed solidarity with the Palestinian people and opposition to Israel.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>2024-04-30 ---- 2024-05-23 ---- 2025-02-05 ---- 2025-04-14 ---- 2025-05-24 ---- 2025-07-20</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Sayda</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LB63</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2025-05-13 ---- 2024-11-07 ---- 2024-10-09</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>May 2025: An education facility was hit when an Israeli drone dropped a stun grenade over it. ---- November 2024: The vicinity of an educational facility was hit by Israeli airstrikes. ---- October 2024: An educational centre of a LNGO was heavily damaged during an attack by suspected Israeli forces on a neighbouring health centre. The centre was providing psychological support and education for over 400 children and is currently not operational due to the damage.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building  ---- Education Building  ---- Education Building </t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Foreign Forces - Military ---- Foreign Forces - Military ---- Foreign Forces - Military</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Israeli Defence Forces ---- Israeli Defence Forces ---- Israeli Defence Forces</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Tasers, Live and Rubber Bullets ---- Aerial Bomb: Plane ---- Aerial Bomb: No Information on Platform Type</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- School: No Further Details</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>LB6</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Explosions/Remote violence ---- Protests ---- Strategic developments ---- Strategic developments</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Air/drone strike ---- Air/drone strike ---- Air/drone strike ---- Shelling/artillery/missile attack ---- Peaceful protest ---- Other ---- Other</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-) ---- Hezbollah ---- Protesters (Palestine) ---- Military Forces of Israel (2022-) ---- Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Refugees/IDPs (Palestine)</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Civilians (Lebanon) ---- Military Forces of Israel (2022-)</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>On 4 October 2024, Israeli warplanes carried out an airstrike targeting an area near the public school in a village on the outskirts of Burj Rahhal town (Tyr, South) amid ongoing hostilities with Hezbollah. Casualties unknown. ---- On 2 November 2024, overnight until the morning, Israeli warplanes carried out airstrikes on buildings and apartments near the Imam Hussein complex in Tyr (Tyr, South). The buildings were completely destroyed. The Israeli army also fired artillery shells. 9 people were killed and 12 others were injured. It also caused serious damage to buildings, residential neighborhoods, infrastructures, streets, electricity, water and telephone networks. A fire broke out twice near the Evangelical School. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 11 November 2024, overnight and until the morning, Israeli warplanes carried out airstrikes on the Ain Al Tutah neighborhood between Burj Rahhal and Aabbassiye (Tyr, South). They also targeted the Qastal School junction, in the Aabbassiye junction. Shops for household electrical equipment were targeted. Casualties unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 24 November 2024, Hezbollah militants fired a guided missile on an Israeli Merkava tank near a school in Jebbayn (Tyr, South). Casualties Unknown. This event is part of what the Israeli army called its 'new phase' of its war on Gaza, amid hostilities against Hezbollah. ---- On 19 December 2024, Palestinian refugees protested in front of the 'Palestine' school in Burj Shemali (Tyr, South) after UNRWA announced the closure of the school. UNRWA also announced that students will be moved to 'Jabalia' school in the refugee camp. ---- Other: On 13 May 2025, an Israeli drone dropped a stun grenade over a school in Ed Dhayra town (Tyr, South). ---- Other: On 15 May 2025, an Israeli drone dropped a stun grenade over a destroyed school in Ed Dhayra town (Tyr, South). There were no casualties.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>2024-10-04 ---- 2024-11-02 ---- 2024-11-11 ---- 2024-11-24 ---- 2024-12-19 ---- 2025-05-13 ---- 2025-05-15</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>Tyr</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>5</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2025-03-10 ---- 2024-11-03 ---- 2024-10-12 ---- 2024-09-25 ---- 2024-03-27</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">March 2025: An educational facility was fired at by Israeli soldiers. The facility had been converted into a service centre following the hostilities between Hezbollah and Israel. ---- November 2024: Near a camp, a UNRWA school was damaged by an Israeli airstrike in the vicinity of the camp.  ---- October 2024: The director of an educational facility was killed by an Israeli airstrike. ---- September 2024: A UN school sustained minor damage, including broken windows from nearby Israeli airstrike blasts. Repairs were underway.  ---- March 2024: A male UN educator was put on administrative leave over possible violations of staff conduct regulations. </t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Education Building  ---- Education Building  ---- Unspecified Location ---- Education Building  ---- Public Building</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Foreign Forces - Military ---- Foreign Forces - Military ---- Foreign Forces - Military ---- Foreign Forces - Military ---- Civilian</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Israeli Defence Forces ---- Israeli Defence Forces ---- Israeli Defence Forces ---- Israeli Defence Forces ---- Partner organisation</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Firearms ---- Aerial Bomb: No Information on Platform Type ---- Aerial Bomb: Plane ---- Aerial Bomb: Plane ---- Not Applicable: No Direct Violence</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>School: No Further Details ---- School: No Further Details ---- Not Applicable ---- School: No Further Details ---- Not Applicable</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1684,22 +3178,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{182CED9A-1673-49AB-8F7D-159B232B16DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70E6B749-14AE-4D1E-AF51-FF515274202A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBAA6A94-9BC7-408A-A156-C8DB31BFE4D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C09DC054-1DCF-4525-BF54-1990A80F8BF4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{240410E9-0B8B-43C7-B80E-D432FBCAA925}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C6F7358-A832-4087-8729-24128EE94D52}"/>
 </file>